--- a/web/Pipistrelli 2024.xlsx
+++ b/web/Pipistrelli 2024.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N129"/>
+  <dimension ref="A1:O129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,6 +491,11 @@
           <t>Provincia</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>provincia</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -550,6 +555,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -604,6 +614,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -658,6 +673,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -717,6 +737,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -776,6 +801,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -835,6 +865,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -894,6 +929,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -953,6 +993,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1056,6 +1101,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1115,6 +1165,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1174,6 +1229,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1228,6 +1288,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1336,6 +1401,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1395,6 +1465,11 @@
           <t>TV</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1547,6 +1622,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1601,6 +1681,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1704,6 +1789,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1758,6 +1848,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1812,6 +1907,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1866,6 +1966,11 @@
           <t>VR</t>
         </is>
       </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>VR</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1923,6 +2028,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1977,6 +2087,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -2036,6 +2151,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -2090,6 +2210,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -2144,6 +2269,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2201,6 +2331,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2255,6 +2390,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -2312,6 +2452,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -2371,6 +2516,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2430,6 +2580,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2484,6 +2639,11 @@
           <t>VR</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>VR</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2593,6 +2753,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -2696,6 +2861,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -2750,6 +2920,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -2809,6 +2984,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -2915,6 +3095,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -2969,6 +3154,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -3018,6 +3208,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -3075,6 +3270,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -3186,6 +3386,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -3243,6 +3448,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -3297,6 +3507,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -3351,6 +3566,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -3408,6 +3628,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -3462,6 +3687,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -3521,6 +3751,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -3578,6 +3813,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -3635,6 +3875,11 @@
           <t>PD</t>
         </is>
       </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -3692,6 +3937,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -3798,6 +4048,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -3852,6 +4107,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -3906,6 +4166,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -3960,6 +4225,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -4014,6 +4284,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -4071,6 +4346,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -4125,6 +4405,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -4179,6 +4464,11 @@
           <t>TV</t>
         </is>
       </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -4233,6 +4523,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -4287,6 +4582,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -4341,6 +4641,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -4395,6 +4700,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -4449,6 +4759,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -4503,6 +4818,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -4557,6 +4877,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -4611,6 +4936,11 @@
           <t>CR</t>
         </is>
       </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -4668,6 +4998,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -4725,6 +5060,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -4779,6 +5119,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -4833,6 +5178,11 @@
           <t>CR</t>
         </is>
       </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -4887,6 +5237,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -4944,6 +5299,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -5003,6 +5363,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -5060,6 +5425,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -5117,6 +5487,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -5171,6 +5546,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -5225,6 +5605,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -5279,6 +5664,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -5333,6 +5723,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -5390,6 +5785,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -5444,6 +5844,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -5498,6 +5903,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -5552,6 +5962,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -5663,6 +6078,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -5820,6 +6240,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -5874,6 +6299,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -5933,6 +6363,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -5987,6 +6422,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -6041,6 +6481,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -6095,6 +6540,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -6154,6 +6604,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -6211,6 +6666,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -6265,6 +6725,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -6319,6 +6784,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -6373,6 +6843,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -6427,6 +6902,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -6481,6 +6961,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -6540,6 +7025,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -6594,6 +7084,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -6648,6 +7143,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -6707,6 +7207,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -6805,6 +7310,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -6864,6 +7374,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -6923,6 +7438,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -6982,6 +7502,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -7036,6 +7561,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -7090,6 +7620,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -7144,6 +7679,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -7198,6 +7738,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -7257,6 +7802,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -7311,6 +7861,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -7370,6 +7925,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -7424,6 +7984,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -7483,6 +8048,11 @@
           <t>VI</t>
         </is>
       </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -7538,6 +8108,11 @@
         <v>11.5501458</v>
       </c>
       <c r="N129" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
